--- a/artfynd/A 62298-2025 artfynd.xlsx
+++ b/artfynd/A 62298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132237169</v>
       </c>
       <c r="B2" t="n">
-        <v>57927</v>
+        <v>57961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132237182</v>
       </c>
       <c r="B3" t="n">
-        <v>58073</v>
+        <v>58107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62298-2025 artfynd.xlsx
+++ b/artfynd/A 62298-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>132237182</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62298-2025 artfynd.xlsx
+++ b/artfynd/A 62298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132237169</v>
       </c>
       <c r="B2" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132237182</v>
       </c>
       <c r="B3" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62298-2025 artfynd.xlsx
+++ b/artfynd/A 62298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132237169</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>132237182</v>
       </c>
       <c r="B3" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
